--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>IG.1103</t>
+          <t>K.1103</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Uhunuulunuu</t>
+          <t>Gnjdi</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U V UIUUAJ</t>
+          <t>DIDDL</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G67G</t>
+          <t>G78B</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52588</v>
+        <v>62369</v>
       </c>
     </row>
     <row r="18">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G78B</t>
+          <t>G78H</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gnjdi</t>
+          <t>Amine</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DIDDL</t>
+          <t>RDAOU</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>1011</v>
@@ -727,7 +727,7 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amine</t>
+          <t>AMINE</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62369.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +703,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1011</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
